--- a/lai/valuationquan/szseinnovation100index.xlsx
+++ b/lai/valuationquan/szseinnovation100index.xlsx
@@ -400,7 +400,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:H1430"/>
+  <dimension ref="A1:H1450"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="9" max="9" width="9.5" bestFit="1" customWidth="1"/>
@@ -33121,7 +33121,7 @@
         <v>3806.216064453125</v>
       </c>
       <c r="F1213">
-        <f t="shared" ref="F1213:F1430" si="10">E1213/1000</f>
+        <f t="shared" ref="F1213:F1450" si="10">E1213/1000</f>
         <v>3.8062160644531251</v>
       </c>
       <c r="G1213">
@@ -38988,6 +38988,546 @@
       </c>
       <c r="H1430">
         <v>34387136</v>
+      </c>
+    </row>
+    <row r="1431" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1431" s="1">
+        <v>46027</v>
+      </c>
+      <c r="B1431">
+        <v>5096.951171875</v>
+      </c>
+      <c r="C1431">
+        <v>5167.26220703125</v>
+      </c>
+      <c r="D1431">
+        <v>5096.951171875</v>
+      </c>
+      <c r="E1431">
+        <v>5165.7138671875</v>
+      </c>
+      <c r="F1431">
+        <f t="shared" si="10"/>
+        <v>5.1657138671874998</v>
+      </c>
+      <c r="G1431">
+        <v>46767088</v>
+      </c>
+      <c r="H1431">
+        <v>46767088</v>
+      </c>
+    </row>
+    <row r="1432" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1432" s="1">
+        <v>46028</v>
+      </c>
+      <c r="B1432">
+        <v>5160.14013671875</v>
+      </c>
+      <c r="C1432">
+        <v>5214.02001953125</v>
+      </c>
+      <c r="D1432">
+        <v>5142.09814453125</v>
+      </c>
+      <c r="E1432">
+        <v>5205.19921875</v>
+      </c>
+      <c r="F1432">
+        <f t="shared" si="10"/>
+        <v>5.2051992187499998</v>
+      </c>
+      <c r="G1432">
+        <v>55262576</v>
+      </c>
+      <c r="H1432">
+        <v>55262576</v>
+      </c>
+    </row>
+    <row r="1433" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1433" s="1">
+        <v>46029</v>
+      </c>
+      <c r="B1433">
+        <v>5213.39892578125</v>
+      </c>
+      <c r="C1433">
+        <v>5253.98779296875</v>
+      </c>
+      <c r="D1433">
+        <v>5183.6591796875</v>
+      </c>
+      <c r="E1433">
+        <v>5225.8720703125</v>
+      </c>
+      <c r="F1433">
+        <f t="shared" si="10"/>
+        <v>5.2258720703124997</v>
+      </c>
+      <c r="G1433">
+        <v>52276444</v>
+      </c>
+      <c r="H1433">
+        <v>52276444</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1434" s="1">
+        <v>46030</v>
+      </c>
+      <c r="B1434">
+        <v>5202.625</v>
+      </c>
+      <c r="C1434">
+        <v>5218.89111328125</v>
+      </c>
+      <c r="D1434">
+        <v>5166.45703125</v>
+      </c>
+      <c r="E1434">
+        <v>5192.85791015625</v>
+      </c>
+      <c r="F1434">
+        <f t="shared" si="10"/>
+        <v>5.19285791015625</v>
+      </c>
+      <c r="G1434">
+        <v>47282492</v>
+      </c>
+      <c r="H1434">
+        <v>47282492</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1435" s="1">
+        <v>46031</v>
+      </c>
+      <c r="B1435">
+        <v>5172.3681640625</v>
+      </c>
+      <c r="C1435">
+        <v>5265.328125</v>
+      </c>
+      <c r="D1435">
+        <v>5169.4580078125</v>
+      </c>
+      <c r="E1435">
+        <v>5250.7158203125</v>
+      </c>
+      <c r="F1435">
+        <f t="shared" si="10"/>
+        <v>5.2507158203125002</v>
+      </c>
+      <c r="G1435">
+        <v>55444084</v>
+      </c>
+      <c r="H1435">
+        <v>55444084</v>
+      </c>
+    </row>
+    <row r="1436" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1436" s="1">
+        <v>46034</v>
+      </c>
+      <c r="B1436">
+        <v>5259.48583984375</v>
+      </c>
+      <c r="C1436">
+        <v>5329.88818359375</v>
+      </c>
+      <c r="D1436">
+        <v>5203.60205078125</v>
+      </c>
+      <c r="E1436">
+        <v>5321.54296875</v>
+      </c>
+      <c r="F1436">
+        <f t="shared" si="10"/>
+        <v>5.3215429687500002</v>
+      </c>
+      <c r="G1436">
+        <v>66006516</v>
+      </c>
+      <c r="H1436">
+        <v>66006516</v>
+      </c>
+    </row>
+    <row r="1437" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1437" s="1">
+        <v>46035</v>
+      </c>
+      <c r="B1437">
+        <v>5330.39990234375</v>
+      </c>
+      <c r="C1437">
+        <v>5353.13916015625</v>
+      </c>
+      <c r="D1437">
+        <v>5193.72802734375</v>
+      </c>
+      <c r="E1437">
+        <v>5213.27783203125</v>
+      </c>
+      <c r="F1437">
+        <f t="shared" si="10"/>
+        <v>5.2132778320312498</v>
+      </c>
+      <c r="G1437">
+        <v>61820708</v>
+      </c>
+      <c r="H1437">
+        <v>61820708</v>
+      </c>
+    </row>
+    <row r="1438" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1438" s="1">
+        <v>46036</v>
+      </c>
+      <c r="B1438">
+        <v>5221.671875</v>
+      </c>
+      <c r="C1438">
+        <v>5310.1220703125</v>
+      </c>
+      <c r="D1438">
+        <v>5173.84521484375</v>
+      </c>
+      <c r="E1438">
+        <v>5231.2880859375</v>
+      </c>
+      <c r="F1438">
+        <f t="shared" si="10"/>
+        <v>5.2312880859374999</v>
+      </c>
+      <c r="G1438">
+        <v>67312840</v>
+      </c>
+      <c r="H1438">
+        <v>67312840</v>
+      </c>
+    </row>
+    <row r="1439" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1439" s="1">
+        <v>46037</v>
+      </c>
+      <c r="B1439">
+        <v>5201.63916015625</v>
+      </c>
+      <c r="C1439">
+        <v>5284.27099609375</v>
+      </c>
+      <c r="D1439">
+        <v>5199.412109375</v>
+      </c>
+      <c r="E1439">
+        <v>5274.35888671875</v>
+      </c>
+      <c r="F1439">
+        <f t="shared" si="10"/>
+        <v>5.2743588867187503</v>
+      </c>
+      <c r="G1439">
+        <v>50301012</v>
+      </c>
+      <c r="H1439">
+        <v>50301012</v>
+      </c>
+    </row>
+    <row r="1440" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1440" s="1">
+        <v>46038</v>
+      </c>
+      <c r="B1440">
+        <v>5327.880859375</v>
+      </c>
+      <c r="C1440">
+        <v>5360.7568359375</v>
+      </c>
+      <c r="D1440">
+        <v>5295.2822265625</v>
+      </c>
+      <c r="E1440">
+        <v>5309.48681640625</v>
+      </c>
+      <c r="F1440">
+        <f t="shared" si="10"/>
+        <v>5.3094868164062499</v>
+      </c>
+      <c r="G1440">
+        <v>50635224</v>
+      </c>
+      <c r="H1440">
+        <v>50635224</v>
+      </c>
+    </row>
+    <row r="1441" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1441" s="1">
+        <v>46041</v>
+      </c>
+      <c r="B1441">
+        <v>5296.19580078125</v>
+      </c>
+      <c r="C1441">
+        <v>5351.744140625</v>
+      </c>
+      <c r="D1441">
+        <v>5282.44580078125</v>
+      </c>
+      <c r="E1441">
+        <v>5305.31494140625</v>
+      </c>
+      <c r="F1441">
+        <f t="shared" si="10"/>
+        <v>5.3053149414062499</v>
+      </c>
+      <c r="G1441">
+        <v>43445092</v>
+      </c>
+      <c r="H1441">
+        <v>43445092</v>
+      </c>
+    </row>
+    <row r="1442" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1442" s="1">
+        <v>46042</v>
+      </c>
+      <c r="B1442">
+        <v>5310.52685546875</v>
+      </c>
+      <c r="C1442">
+        <v>5312.94677734375</v>
+      </c>
+      <c r="D1442">
+        <v>5190.84814453125</v>
+      </c>
+      <c r="E1442">
+        <v>5216.80322265625</v>
+      </c>
+      <c r="F1442">
+        <f t="shared" si="10"/>
+        <v>5.2168032226562504</v>
+      </c>
+      <c r="G1442">
+        <v>44435668</v>
+      </c>
+      <c r="H1442">
+        <v>44435668</v>
+      </c>
+    </row>
+    <row r="1443" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1443" s="1">
+        <v>46043</v>
+      </c>
+      <c r="B1443">
+        <v>5202.740234375</v>
+      </c>
+      <c r="C1443">
+        <v>5296.4521484375</v>
+      </c>
+      <c r="D1443">
+        <v>5202.740234375</v>
+      </c>
+      <c r="E1443">
+        <v>5247.39111328125</v>
+      </c>
+      <c r="F1443">
+        <f t="shared" si="10"/>
+        <v>5.2473911132812496</v>
+      </c>
+      <c r="G1443">
+        <v>37996984</v>
+      </c>
+      <c r="H1443">
+        <v>37996984</v>
+      </c>
+    </row>
+    <row r="1444" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1444" s="1">
+        <v>46044</v>
+      </c>
+      <c r="B1444">
+        <v>5280.69677734375</v>
+      </c>
+      <c r="C1444">
+        <v>5304.18115234375</v>
+      </c>
+      <c r="D1444">
+        <v>5206.6181640625</v>
+      </c>
+      <c r="E1444">
+        <v>5264.64599609375</v>
+      </c>
+      <c r="F1444">
+        <f t="shared" si="10"/>
+        <v>5.2646459960937504</v>
+      </c>
+      <c r="G1444">
+        <v>38820684</v>
+      </c>
+      <c r="H1444">
+        <v>38820684</v>
+      </c>
+    </row>
+    <row r="1445" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1445" s="1">
+        <v>46045</v>
+      </c>
+      <c r="B1445">
+        <v>5267.63720703125</v>
+      </c>
+      <c r="C1445">
+        <v>5281.8359375</v>
+      </c>
+      <c r="D1445">
+        <v>5230.48193359375</v>
+      </c>
+      <c r="E1445">
+        <v>5280.89111328125</v>
+      </c>
+      <c r="F1445">
+        <f t="shared" si="10"/>
+        <v>5.2808911132812497</v>
+      </c>
+      <c r="G1445">
+        <v>47842816</v>
+      </c>
+      <c r="H1445">
+        <v>47842816</v>
+      </c>
+    </row>
+    <row r="1446" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1446" s="1">
+        <v>46048</v>
+      </c>
+      <c r="B1446">
+        <v>5290.59423828125</v>
+      </c>
+      <c r="C1446">
+        <v>5290.59423828125</v>
+      </c>
+      <c r="D1446">
+        <v>5188.9970703125</v>
+      </c>
+      <c r="E1446">
+        <v>5202.44287109375</v>
+      </c>
+      <c r="F1446">
+        <f t="shared" si="10"/>
+        <v>5.2024428710937496</v>
+      </c>
+      <c r="G1446">
+        <v>47017984</v>
+      </c>
+      <c r="H1446">
+        <v>47017984</v>
+      </c>
+    </row>
+    <row r="1447" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1447" s="1">
+        <v>46049</v>
+      </c>
+      <c r="B1447">
+        <v>5202.666015625</v>
+      </c>
+      <c r="C1447">
+        <v>5266.28515625</v>
+      </c>
+      <c r="D1447">
+        <v>5139.89501953125</v>
+      </c>
+      <c r="E1447">
+        <v>5230.09619140625</v>
+      </c>
+      <c r="F1447">
+        <f t="shared" si="10"/>
+        <v>5.2300961914062496</v>
+      </c>
+      <c r="G1447">
+        <v>38618496</v>
+      </c>
+      <c r="H1447">
+        <v>38618496</v>
+      </c>
+    </row>
+    <row r="1448" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1448" s="1">
+        <v>46050</v>
+      </c>
+      <c r="B1448">
+        <v>5242.52294921875</v>
+      </c>
+      <c r="C1448">
+        <v>5245.49609375</v>
+      </c>
+      <c r="D1448">
+        <v>5165.80419921875</v>
+      </c>
+      <c r="E1448">
+        <v>5216.02587890625</v>
+      </c>
+      <c r="F1448">
+        <f t="shared" si="10"/>
+        <v>5.2160258789062501</v>
+      </c>
+      <c r="G1448">
+        <v>37877596</v>
+      </c>
+      <c r="H1448">
+        <v>37877596</v>
+      </c>
+    </row>
+    <row r="1449" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1449" s="1">
+        <v>46051</v>
+      </c>
+      <c r="B1449">
+        <v>5211.826171875</v>
+      </c>
+      <c r="C1449">
+        <v>5223.1572265625</v>
+      </c>
+      <c r="D1449">
+        <v>5137.35791015625</v>
+      </c>
+      <c r="E1449">
+        <v>5147.16796875</v>
+      </c>
+      <c r="F1449">
+        <f t="shared" si="10"/>
+        <v>5.1471679687499998</v>
+      </c>
+      <c r="G1449">
+        <v>41004388</v>
+      </c>
+      <c r="H1449">
+        <v>41004388</v>
+      </c>
+    </row>
+    <row r="1450" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1450" s="1">
+        <v>46052</v>
+      </c>
+      <c r="B1450">
+        <v>5138.98486328125</v>
+      </c>
+      <c r="C1450">
+        <v>5207.64013671875</v>
+      </c>
+      <c r="D1450">
+        <v>5060.33984375</v>
+      </c>
+      <c r="E1450">
+        <v>5174.1728515625</v>
+      </c>
+      <c r="F1450">
+        <f t="shared" si="10"/>
+        <v>5.1741728515625001</v>
+      </c>
+      <c r="G1450">
+        <v>36634656</v>
+      </c>
+      <c r="H1450">
+        <v>36634656</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100index.xlsx
+++ b/lai/valuationquan/szseinnovation100index.xlsx
@@ -400,7 +400,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:H1450"/>
+  <dimension ref="A1:H1464"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="9" max="9" width="9.5" bestFit="1" customWidth="1"/>
@@ -33121,7 +33121,7 @@
         <v>3806.216064453125</v>
       </c>
       <c r="F1213">
-        <f t="shared" ref="F1213:F1450" si="10">E1213/1000</f>
+        <f t="shared" ref="F1213:F1464" si="10">E1213/1000</f>
         <v>3.8062160644531251</v>
       </c>
       <c r="G1213">
@@ -39528,6 +39528,384 @@
       </c>
       <c r="H1450">
         <v>36634656</v>
+      </c>
+    </row>
+    <row r="1451" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1451" s="1">
+        <v>46055</v>
+      </c>
+      <c r="B1451">
+        <v>5159.73681640625</v>
+      </c>
+      <c r="C1451">
+        <v>5190.2412109375</v>
+      </c>
+      <c r="D1451">
+        <v>5032.7080078125</v>
+      </c>
+      <c r="E1451">
+        <v>5034.77197265625</v>
+      </c>
+      <c r="F1451">
+        <f t="shared" si="10"/>
+        <v>5.0347719726562499</v>
+      </c>
+      <c r="G1451">
+        <v>32023270</v>
+      </c>
+      <c r="H1451">
+        <v>32023270</v>
+      </c>
+    </row>
+    <row r="1452" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1452" s="1">
+        <v>46056</v>
+      </c>
+      <c r="B1452">
+        <v>5086.8662109375</v>
+      </c>
+      <c r="C1452">
+        <v>5116.162109375</v>
+      </c>
+      <c r="D1452">
+        <v>5014.23486328125</v>
+      </c>
+      <c r="E1452">
+        <v>5114.71484375</v>
+      </c>
+      <c r="F1452">
+        <f t="shared" si="10"/>
+        <v>5.1147148437499999</v>
+      </c>
+      <c r="G1452">
+        <v>31650404</v>
+      </c>
+      <c r="H1452">
+        <v>31650404</v>
+      </c>
+    </row>
+    <row r="1453" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1453" s="1">
+        <v>46057</v>
+      </c>
+      <c r="B1453">
+        <v>5083.1171875</v>
+      </c>
+      <c r="C1453">
+        <v>5129.97998046875</v>
+      </c>
+      <c r="D1453">
+        <v>5034.51904296875</v>
+      </c>
+      <c r="E1453">
+        <v>5122.9208984375</v>
+      </c>
+      <c r="F1453">
+        <f t="shared" si="10"/>
+        <v>5.1229208984375001</v>
+      </c>
+      <c r="G1453">
+        <v>29554770</v>
+      </c>
+      <c r="H1453">
+        <v>29554770</v>
+      </c>
+    </row>
+    <row r="1454" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1454" s="1">
+        <v>46058</v>
+      </c>
+      <c r="B1454">
+        <v>5090.69091796875</v>
+      </c>
+      <c r="C1454">
+        <v>5106.9912109375</v>
+      </c>
+      <c r="D1454">
+        <v>5034.55419921875</v>
+      </c>
+      <c r="E1454">
+        <v>5065.39990234375</v>
+      </c>
+      <c r="F1454">
+        <f t="shared" si="10"/>
+        <v>5.0653999023437501</v>
+      </c>
+      <c r="G1454">
+        <v>26695780</v>
+      </c>
+      <c r="H1454">
+        <v>26695780</v>
+      </c>
+    </row>
+    <row r="1455" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1455" s="1">
+        <v>46059</v>
+      </c>
+      <c r="B1455">
+        <v>5015.5771484375</v>
+      </c>
+      <c r="C1455">
+        <v>5106.00390625</v>
+      </c>
+      <c r="D1455">
+        <v>4991.26904296875</v>
+      </c>
+      <c r="E1455">
+        <v>5046.0869140625</v>
+      </c>
+      <c r="F1455">
+        <f t="shared" si="10"/>
+        <v>5.0460869140625002</v>
+      </c>
+      <c r="G1455">
+        <v>25919942</v>
+      </c>
+      <c r="H1455">
+        <v>25919942</v>
+      </c>
+    </row>
+    <row r="1456" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1456" s="1">
+        <v>46062</v>
+      </c>
+      <c r="B1456">
+        <v>5114.43408203125</v>
+      </c>
+      <c r="C1456">
+        <v>5152.4677734375</v>
+      </c>
+      <c r="D1456">
+        <v>5081.84423828125</v>
+      </c>
+      <c r="E1456">
+        <v>5147.97119140625</v>
+      </c>
+      <c r="F1456">
+        <f t="shared" si="10"/>
+        <v>5.14797119140625</v>
+      </c>
+      <c r="G1456">
+        <v>27594854</v>
+      </c>
+      <c r="H1456">
+        <v>27594854</v>
+      </c>
+    </row>
+    <row r="1457" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1457" s="1">
+        <v>46063</v>
+      </c>
+      <c r="B1457">
+        <v>5138.7431640625</v>
+      </c>
+      <c r="C1457">
+        <v>5180.38916015625</v>
+      </c>
+      <c r="D1457">
+        <v>5135.27099609375</v>
+      </c>
+      <c r="E1457">
+        <v>5153.2138671875</v>
+      </c>
+      <c r="F1457">
+        <f t="shared" si="10"/>
+        <v>5.1532138671874996</v>
+      </c>
+      <c r="G1457">
+        <v>26336498</v>
+      </c>
+      <c r="H1457">
+        <v>26336498</v>
+      </c>
+    </row>
+    <row r="1458" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1458" s="1">
+        <v>46064</v>
+      </c>
+      <c r="B1458">
+        <v>5143.14306640625</v>
+      </c>
+      <c r="C1458">
+        <v>5154.09716796875</v>
+      </c>
+      <c r="D1458">
+        <v>5107.60791015625</v>
+      </c>
+      <c r="E1458">
+        <v>5112.7490234375</v>
+      </c>
+      <c r="F1458">
+        <f t="shared" si="10"/>
+        <v>5.1127490234374999</v>
+      </c>
+      <c r="G1458">
+        <v>22846364</v>
+      </c>
+      <c r="H1458">
+        <v>22846364</v>
+      </c>
+    </row>
+    <row r="1459" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1459" s="1">
+        <v>46065</v>
+      </c>
+      <c r="B1459">
+        <v>5126.06982421875</v>
+      </c>
+      <c r="C1459">
+        <v>5178.23779296875</v>
+      </c>
+      <c r="D1459">
+        <v>5123.27978515625</v>
+      </c>
+      <c r="E1459">
+        <v>5171.791015625</v>
+      </c>
+      <c r="F1459">
+        <f t="shared" si="10"/>
+        <v>5.1717910156249998</v>
+      </c>
+      <c r="G1459">
+        <v>26190720</v>
+      </c>
+      <c r="H1459">
+        <v>26190720</v>
+      </c>
+    </row>
+    <row r="1460" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1460" s="1">
+        <v>46066</v>
+      </c>
+      <c r="B1460">
+        <v>5143.64404296875</v>
+      </c>
+      <c r="C1460">
+        <v>5167.92578125</v>
+      </c>
+      <c r="D1460">
+        <v>5112.833984375</v>
+      </c>
+      <c r="E1460">
+        <v>5112.833984375</v>
+      </c>
+      <c r="F1460">
+        <f t="shared" si="10"/>
+        <v>5.1128339843750004</v>
+      </c>
+      <c r="G1460">
+        <v>24415572</v>
+      </c>
+      <c r="H1460">
+        <v>24415572</v>
+      </c>
+    </row>
+    <row r="1461" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1461" s="1">
+        <v>46077</v>
+      </c>
+      <c r="B1461">
+        <v>5190.0458984375</v>
+      </c>
+      <c r="C1461">
+        <v>5195.52001953125</v>
+      </c>
+      <c r="D1461">
+        <v>5134.7822265625</v>
+      </c>
+      <c r="E1461">
+        <v>5153.9580078125</v>
+      </c>
+      <c r="F1461">
+        <f t="shared" si="10"/>
+        <v>5.1539580078125002</v>
+      </c>
+      <c r="G1461">
+        <v>26802938</v>
+      </c>
+      <c r="H1461">
+        <v>26802938</v>
+      </c>
+    </row>
+    <row r="1462" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1462" s="1">
+        <v>46078</v>
+      </c>
+      <c r="B1462">
+        <v>5162.34912109375</v>
+      </c>
+      <c r="C1462">
+        <v>5219.81396484375</v>
+      </c>
+      <c r="D1462">
+        <v>5151.251953125</v>
+      </c>
+      <c r="E1462">
+        <v>5204.31396484375</v>
+      </c>
+      <c r="F1462">
+        <f t="shared" si="10"/>
+        <v>5.2043139648437498</v>
+      </c>
+      <c r="G1462">
+        <v>30549650</v>
+      </c>
+      <c r="H1462">
+        <v>30549650</v>
+      </c>
+    </row>
+    <row r="1463" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1463" s="1">
+        <v>46079</v>
+      </c>
+      <c r="B1463">
+        <v>5198.4208984375</v>
+      </c>
+      <c r="C1463">
+        <v>5198.44287109375</v>
+      </c>
+      <c r="D1463">
+        <v>5149.869140625</v>
+      </c>
+      <c r="E1463">
+        <v>5184.98876953125</v>
+      </c>
+      <c r="F1463">
+        <f t="shared" si="10"/>
+        <v>5.18498876953125</v>
+      </c>
+      <c r="G1463">
+        <v>33669680</v>
+      </c>
+      <c r="H1463">
+        <v>33669680</v>
+      </c>
+    </row>
+    <row r="1464" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1464" s="1">
+        <v>46080</v>
+      </c>
+      <c r="B1464">
+        <v>5143.455078125</v>
+      </c>
+      <c r="C1464">
+        <v>5153.10205078125</v>
+      </c>
+      <c r="D1464">
+        <v>5106.73095703125</v>
+      </c>
+      <c r="E1464">
+        <v>5120.02685546875</v>
+      </c>
+      <c r="F1464">
+        <f t="shared" si="10"/>
+        <v>5.1200268554687502</v>
+      </c>
+      <c r="G1464">
+        <v>30557054</v>
+      </c>
+      <c r="H1464">
+        <v>30557054</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100index.xlsx
+++ b/lai/valuationquan/szseinnovation100index.xlsx
@@ -400,7 +400,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:H1464"/>
+  <dimension ref="A1:H1486"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="9" max="9" width="9.5" bestFit="1" customWidth="1"/>
@@ -33121,7 +33121,7 @@
         <v>3806.216064453125</v>
       </c>
       <c r="F1213">
-        <f t="shared" ref="F1213:F1464" si="10">E1213/1000</f>
+        <f t="shared" ref="F1213:F1467" si="10">E1213/1000</f>
         <v>3.8062160644531251</v>
       </c>
       <c r="G1213">
@@ -39906,6 +39906,600 @@
       </c>
       <c r="H1464">
         <v>30557054</v>
+      </c>
+    </row>
+    <row r="1465" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1465" s="1">
+        <v>46083</v>
+      </c>
+      <c r="B1465">
+        <v>5054.40087890625</v>
+      </c>
+      <c r="C1465">
+        <v>5167.2451171875</v>
+      </c>
+      <c r="D1465">
+        <v>5052.634765625</v>
+      </c>
+      <c r="E1465">
+        <v>5142.8720703125</v>
+      </c>
+      <c r="F1465">
+        <f t="shared" si="10"/>
+        <v>5.1428720703125004</v>
+      </c>
+      <c r="G1465">
+        <v>38856504</v>
+      </c>
+      <c r="H1465">
+        <v>38856504</v>
+      </c>
+    </row>
+    <row r="1466" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1466" s="1">
+        <v>46084</v>
+      </c>
+      <c r="B1466">
+        <v>5163.01123046875</v>
+      </c>
+      <c r="C1466">
+        <v>5189.60205078125</v>
+      </c>
+      <c r="D1466">
+        <v>5003.7490234375</v>
+      </c>
+      <c r="E1466">
+        <v>5005.42578125</v>
+      </c>
+      <c r="F1466">
+        <f t="shared" si="10"/>
+        <v>5.0054257812499996</v>
+      </c>
+      <c r="G1466">
+        <v>39509688</v>
+      </c>
+      <c r="H1466">
+        <v>39509688</v>
+      </c>
+    </row>
+    <row r="1467" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1467" s="1">
+        <v>46085</v>
+      </c>
+      <c r="B1467">
+        <v>4946.81982421875</v>
+      </c>
+      <c r="C1467">
+        <v>5022.8740234375</v>
+      </c>
+      <c r="D1467">
+        <v>4928.1728515625</v>
+      </c>
+      <c r="E1467">
+        <v>4958.490234375</v>
+      </c>
+      <c r="F1467">
+        <f t="shared" si="10"/>
+        <v>4.9584902343749997</v>
+      </c>
+      <c r="G1467">
+        <v>27136472</v>
+      </c>
+      <c r="H1467">
+        <v>27136472</v>
+      </c>
+    </row>
+    <row r="1468" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1468" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B1468">
+        <v>5047.22705078125</v>
+      </c>
+      <c r="C1468">
+        <v>5080.9140625</v>
+      </c>
+      <c r="D1468">
+        <v>4996.52099609375</v>
+      </c>
+      <c r="E1468">
+        <v>5027.0078125</v>
+      </c>
+      <c r="F1468">
+        <f t="shared" ref="F1468:F1486" si="11">E1468/1000</f>
+        <v>5.0270078125</v>
+      </c>
+      <c r="G1468">
+        <v>26187468</v>
+      </c>
+      <c r="H1468">
+        <v>26187468</v>
+      </c>
+    </row>
+    <row r="1469" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1469" s="1">
+        <v>46087</v>
+      </c>
+      <c r="B1469">
+        <v>5010.2578125</v>
+      </c>
+      <c r="C1469">
+        <v>5071.18212890625</v>
+      </c>
+      <c r="D1469">
+        <v>4989.3837890625</v>
+      </c>
+      <c r="E1469">
+        <v>5040.837890625</v>
+      </c>
+      <c r="F1469">
+        <f t="shared" si="11"/>
+        <v>5.0408378906250002</v>
+      </c>
+      <c r="G1469">
+        <v>22881356</v>
+      </c>
+      <c r="H1469">
+        <v>22881356</v>
+      </c>
+    </row>
+    <row r="1470" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1470" s="1">
+        <v>46090</v>
+      </c>
+      <c r="B1470">
+        <v>4933.0087890625</v>
+      </c>
+      <c r="C1470">
+        <v>5008.92578125</v>
+      </c>
+      <c r="D1470">
+        <v>4867.36083984375</v>
+      </c>
+      <c r="E1470">
+        <v>4995.44384765625</v>
+      </c>
+      <c r="F1470">
+        <f t="shared" si="11"/>
+        <v>4.9954438476562499</v>
+      </c>
+      <c r="G1470">
+        <v>29776686</v>
+      </c>
+      <c r="H1470">
+        <v>29776686</v>
+      </c>
+    </row>
+    <row r="1471" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1471" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B1471">
+        <v>5079.9072265625</v>
+      </c>
+      <c r="C1471">
+        <v>5122.19921875</v>
+      </c>
+      <c r="D1471">
+        <v>5074.0400390625</v>
+      </c>
+      <c r="E1471">
+        <v>5120.22802734375</v>
+      </c>
+      <c r="F1471">
+        <f t="shared" si="11"/>
+        <v>5.1202280273437504</v>
+      </c>
+      <c r="G1471">
+        <v>25581736</v>
+      </c>
+      <c r="H1471">
+        <v>25581736</v>
+      </c>
+    </row>
+    <row r="1472" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1472" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B1472">
+        <v>5142.330078125</v>
+      </c>
+      <c r="C1472">
+        <v>5249.5869140625</v>
+      </c>
+      <c r="D1472">
+        <v>5142.330078125</v>
+      </c>
+      <c r="E1472">
+        <v>5202.3251953125</v>
+      </c>
+      <c r="F1472">
+        <f t="shared" si="11"/>
+        <v>5.2023251953124996</v>
+      </c>
+      <c r="G1472">
+        <v>31609404</v>
+      </c>
+      <c r="H1472">
+        <v>31609404</v>
+      </c>
+    </row>
+    <row r="1473" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1473" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B1473">
+        <v>5200.41015625</v>
+      </c>
+      <c r="C1473">
+        <v>5213.4521484375</v>
+      </c>
+      <c r="D1473">
+        <v>5123.12109375</v>
+      </c>
+      <c r="E1473">
+        <v>5161.24609375</v>
+      </c>
+      <c r="F1473">
+        <f t="shared" si="11"/>
+        <v>5.16124609375</v>
+      </c>
+      <c r="G1473">
+        <v>27839080</v>
+      </c>
+      <c r="H1473">
+        <v>27839080</v>
+      </c>
+    </row>
+    <row r="1474" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1474" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B1474">
+        <v>5126.10107421875</v>
+      </c>
+      <c r="C1474">
+        <v>5175.01904296875</v>
+      </c>
+      <c r="D1474">
+        <v>5115.5419921875</v>
+      </c>
+      <c r="E1474">
+        <v>5128.02099609375</v>
+      </c>
+      <c r="F1474">
+        <f t="shared" si="11"/>
+        <v>5.12802099609375</v>
+      </c>
+      <c r="G1474">
+        <v>26949056</v>
+      </c>
+      <c r="H1474">
+        <v>26949056</v>
+      </c>
+    </row>
+    <row r="1475" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1475" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B1475">
+        <v>5137.02880859375</v>
+      </c>
+      <c r="C1475">
+        <v>5174.81201171875</v>
+      </c>
+      <c r="D1475">
+        <v>5063.91796875</v>
+      </c>
+      <c r="E1475">
+        <v>5170.6650390625</v>
+      </c>
+      <c r="F1475">
+        <f t="shared" si="11"/>
+        <v>5.1706650390625004</v>
+      </c>
+      <c r="G1475">
+        <v>26424188</v>
+      </c>
+      <c r="H1475">
+        <v>26424188</v>
+      </c>
+    </row>
+    <row r="1476" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1476" s="1">
+        <v>46098</v>
+      </c>
+      <c r="B1476">
+        <v>5209.06689453125</v>
+      </c>
+      <c r="C1476">
+        <v>5221.3720703125</v>
+      </c>
+      <c r="D1476">
+        <v>5082.2158203125</v>
+      </c>
+      <c r="E1476">
+        <v>5082.2158203125</v>
+      </c>
+      <c r="F1476">
+        <f t="shared" si="11"/>
+        <v>5.0822158203125003</v>
+      </c>
+      <c r="G1476">
+        <v>27268242</v>
+      </c>
+      <c r="H1476">
+        <v>27268242</v>
+      </c>
+    </row>
+    <row r="1477" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1477" s="1">
+        <v>46099</v>
+      </c>
+      <c r="B1477">
+        <v>5104.39404296875</v>
+      </c>
+      <c r="C1477">
+        <v>5151.4990234375</v>
+      </c>
+      <c r="D1477">
+        <v>5056.748046875</v>
+      </c>
+      <c r="E1477">
+        <v>5145.6240234375</v>
+      </c>
+      <c r="F1477">
+        <f t="shared" si="11"/>
+        <v>5.1456240234374997</v>
+      </c>
+      <c r="G1477">
+        <v>22926718</v>
+      </c>
+      <c r="H1477">
+        <v>22926718</v>
+      </c>
+    </row>
+    <row r="1478" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1478" s="1">
+        <v>46100</v>
+      </c>
+      <c r="B1478">
+        <v>5089.3359375</v>
+      </c>
+      <c r="C1478">
+        <v>5138.12890625</v>
+      </c>
+      <c r="D1478">
+        <v>5045.84521484375</v>
+      </c>
+      <c r="E1478">
+        <v>5061.2587890625</v>
+      </c>
+      <c r="F1478">
+        <f t="shared" si="11"/>
+        <v>5.0612587890625003</v>
+      </c>
+      <c r="G1478">
+        <v>23459946</v>
+      </c>
+      <c r="H1478">
+        <v>23459946</v>
+      </c>
+    </row>
+    <row r="1479" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1479" s="1">
+        <v>46101</v>
+      </c>
+      <c r="B1479">
+        <v>5109.6669921875</v>
+      </c>
+      <c r="C1479">
+        <v>5176.9208984375</v>
+      </c>
+      <c r="D1479">
+        <v>5076.43701171875</v>
+      </c>
+      <c r="E1479">
+        <v>5081.205078125</v>
+      </c>
+      <c r="F1479">
+        <f t="shared" si="11"/>
+        <v>5.0812050781250004</v>
+      </c>
+      <c r="G1479">
+        <v>29305992</v>
+      </c>
+      <c r="H1479">
+        <v>29305992</v>
+      </c>
+    </row>
+    <row r="1480" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1480" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1480">
+        <v>5010.57421875</v>
+      </c>
+      <c r="C1480">
+        <v>5056.10791015625</v>
+      </c>
+      <c r="D1480">
+        <v>4889.80712890625</v>
+      </c>
+      <c r="E1480">
+        <v>4916.7109375</v>
+      </c>
+      <c r="F1480">
+        <f t="shared" si="11"/>
+        <v>4.9167109375000004</v>
+      </c>
+      <c r="G1480">
+        <v>33300320</v>
+      </c>
+      <c r="H1480">
+        <v>33300320</v>
+      </c>
+    </row>
+    <row r="1481" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1481" s="1">
+        <v>46105</v>
+      </c>
+      <c r="B1481">
+        <v>4971.5771484375</v>
+      </c>
+      <c r="C1481">
+        <v>4974.5341796875</v>
+      </c>
+      <c r="D1481">
+        <v>4824.47216796875</v>
+      </c>
+      <c r="E1481">
+        <v>4944.44287109375</v>
+      </c>
+      <c r="F1481">
+        <f t="shared" si="11"/>
+        <v>4.9444428710937496</v>
+      </c>
+      <c r="G1481">
+        <v>24725590</v>
+      </c>
+      <c r="H1481">
+        <v>24725590</v>
+      </c>
+    </row>
+    <row r="1482" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1482" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B1482">
+        <v>4982.44921875</v>
+      </c>
+      <c r="C1482">
+        <v>5046.8671875</v>
+      </c>
+      <c r="D1482">
+        <v>4978.56787109375</v>
+      </c>
+      <c r="E1482">
+        <v>5035.7919921875</v>
+      </c>
+      <c r="F1482">
+        <f t="shared" si="11"/>
+        <v>5.0357919921874998</v>
+      </c>
+      <c r="G1482">
+        <v>24491250</v>
+      </c>
+      <c r="H1482">
+        <v>24491250</v>
+      </c>
+    </row>
+    <row r="1483" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1483" s="1">
+        <v>46107</v>
+      </c>
+      <c r="B1483">
+        <v>5018.0771484375</v>
+      </c>
+      <c r="C1483">
+        <v>5068.56689453125</v>
+      </c>
+      <c r="D1483">
+        <v>4952.27392578125</v>
+      </c>
+      <c r="E1483">
+        <v>4961.01318359375</v>
+      </c>
+      <c r="F1483">
+        <f t="shared" si="11"/>
+        <v>4.9610131835937503</v>
+      </c>
+      <c r="G1483">
+        <v>21615848</v>
+      </c>
+      <c r="H1483">
+        <v>21615848</v>
+      </c>
+    </row>
+    <row r="1484" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1484" s="1">
+        <v>46108</v>
+      </c>
+      <c r="B1484">
+        <v>4914.0078125</v>
+      </c>
+      <c r="C1484">
+        <v>5034.40087890625</v>
+      </c>
+      <c r="D1484">
+        <v>4909.43798828125</v>
+      </c>
+      <c r="E1484">
+        <v>5003.3837890625</v>
+      </c>
+      <c r="F1484">
+        <f t="shared" si="11"/>
+        <v>5.0033837890625001</v>
+      </c>
+      <c r="G1484">
+        <v>21322248</v>
+      </c>
+      <c r="H1484">
+        <v>21322248</v>
+      </c>
+    </row>
+    <row r="1485" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1485" s="1">
+        <v>46111</v>
+      </c>
+      <c r="B1485">
+        <v>4939.02197265625</v>
+      </c>
+      <c r="C1485">
+        <v>4975.06787109375</v>
+      </c>
+      <c r="D1485">
+        <v>4897.4140625</v>
+      </c>
+      <c r="E1485">
+        <v>4969.27001953125</v>
+      </c>
+      <c r="F1485">
+        <f t="shared" si="11"/>
+        <v>4.9692700195312502</v>
+      </c>
+      <c r="G1485">
+        <v>22274196</v>
+      </c>
+      <c r="H1485">
+        <v>22274196</v>
+      </c>
+    </row>
+    <row r="1486" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1486" s="1">
+        <v>46112</v>
+      </c>
+      <c r="B1486">
+        <v>4964.5029296875</v>
+      </c>
+      <c r="C1486">
+        <v>5014.537109375</v>
+      </c>
+      <c r="D1486">
+        <v>4885.1591796875</v>
+      </c>
+      <c r="E1486">
+        <v>4885.1591796875</v>
+      </c>
+      <c r="F1486">
+        <f t="shared" si="11"/>
+        <v>4.8851591796875002</v>
+      </c>
+      <c r="G1486">
+        <v>22858600</v>
+      </c>
+      <c r="H1486">
+        <v>22858600</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100index.xlsx
+++ b/lai/valuationquan/szseinnovation100index.xlsx
@@ -400,7 +400,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:H1486"/>
+  <dimension ref="A1:H1507"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="9" max="9" width="9.5" bestFit="1" customWidth="1"/>
@@ -40006,7 +40006,7 @@
         <v>5027.0078125</v>
       </c>
       <c r="F1468">
-        <f t="shared" ref="F1468:F1486" si="11">E1468/1000</f>
+        <f t="shared" ref="F1468:F1507" si="11">E1468/1000</f>
         <v>5.0270078125</v>
       </c>
       <c r="G1468">
@@ -40500,6 +40500,573 @@
       </c>
       <c r="H1486">
         <v>22858600</v>
+      </c>
+    </row>
+    <row r="1487" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1487" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B1487">
+        <v>4964.6171875</v>
+      </c>
+      <c r="C1487">
+        <v>4965.703125</v>
+      </c>
+      <c r="D1487">
+        <v>4904.14306640625</v>
+      </c>
+      <c r="E1487">
+        <v>4954.28515625</v>
+      </c>
+      <c r="F1487">
+        <f t="shared" si="11"/>
+        <v>4.9542851562500001</v>
+      </c>
+      <c r="G1487">
+        <v>23690092</v>
+      </c>
+      <c r="H1487">
+        <v>23690092</v>
+      </c>
+    </row>
+    <row r="1488" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1488" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B1488">
+        <v>4936.56201171875</v>
+      </c>
+      <c r="C1488">
+        <v>4937.2919921875</v>
+      </c>
+      <c r="D1488">
+        <v>4827.666015625</v>
+      </c>
+      <c r="E1488">
+        <v>4851.6728515625</v>
+      </c>
+      <c r="F1488">
+        <f t="shared" si="11"/>
+        <v>4.8516728515625003</v>
+      </c>
+      <c r="G1488">
+        <v>22419428</v>
+      </c>
+      <c r="H1488">
+        <v>22419428</v>
+      </c>
+    </row>
+    <row r="1489" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1489" s="1">
+        <v>46115</v>
+      </c>
+      <c r="B1489">
+        <v>4878.833984375</v>
+      </c>
+      <c r="C1489">
+        <v>4883.18603515625</v>
+      </c>
+      <c r="D1489">
+        <v>4801.44677734375</v>
+      </c>
+      <c r="E1489">
+        <v>4803.134765625</v>
+      </c>
+      <c r="F1489">
+        <f t="shared" si="11"/>
+        <v>4.8031347656249999</v>
+      </c>
+      <c r="G1489">
+        <v>19125416</v>
+      </c>
+      <c r="H1489">
+        <v>19125416</v>
+      </c>
+    </row>
+    <row r="1490" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1490" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B1490">
+        <v>4821.2822265625</v>
+      </c>
+      <c r="C1490">
+        <v>4849.18017578125</v>
+      </c>
+      <c r="D1490">
+        <v>4773.87109375</v>
+      </c>
+      <c r="E1490">
+        <v>4810.39794921875</v>
+      </c>
+      <c r="F1490">
+        <f t="shared" si="11"/>
+        <v>4.8103979492187499</v>
+      </c>
+      <c r="G1490">
+        <v>18438860</v>
+      </c>
+      <c r="H1490">
+        <v>18438860</v>
+      </c>
+    </row>
+    <row r="1491" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1491" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B1491">
+        <v>4942.162109375</v>
+      </c>
+      <c r="C1491">
+        <v>5051.18798828125</v>
+      </c>
+      <c r="D1491">
+        <v>4926.60693359375</v>
+      </c>
+      <c r="E1491">
+        <v>5051.046875</v>
+      </c>
+      <c r="F1491">
+        <f t="shared" si="11"/>
+        <v>5.0510468749999999</v>
+      </c>
+      <c r="G1491">
+        <v>32126302</v>
+      </c>
+      <c r="H1491">
+        <v>32126302</v>
+      </c>
+    </row>
+    <row r="1492" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1492" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B1492">
+        <v>5009.0830078125</v>
+      </c>
+      <c r="C1492">
+        <v>5058.10009765625</v>
+      </c>
+      <c r="D1492">
+        <v>4994.0419921875</v>
+      </c>
+      <c r="E1492">
+        <v>5039.15478515625</v>
+      </c>
+      <c r="F1492">
+        <f t="shared" si="11"/>
+        <v>5.0391547851562501</v>
+      </c>
+      <c r="G1492">
+        <v>26481902</v>
+      </c>
+      <c r="H1492">
+        <v>26481902</v>
+      </c>
+    </row>
+    <row r="1493" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1493" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B1493">
+        <v>5082.85888671875</v>
+      </c>
+      <c r="C1493">
+        <v>5231.51513671875</v>
+      </c>
+      <c r="D1493">
+        <v>5082.85888671875</v>
+      </c>
+      <c r="E1493">
+        <v>5205.2890625</v>
+      </c>
+      <c r="F1493">
+        <f t="shared" si="11"/>
+        <v>5.2052890625000003</v>
+      </c>
+      <c r="G1493">
+        <v>36677276</v>
+      </c>
+      <c r="H1493">
+        <v>36677276</v>
+      </c>
+    </row>
+    <row r="1494" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1494" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B1494">
+        <v>5185.89111328125</v>
+      </c>
+      <c r="C1494">
+        <v>5260.93505859375</v>
+      </c>
+      <c r="D1494">
+        <v>5185.89111328125</v>
+      </c>
+      <c r="E1494">
+        <v>5243.14013671875</v>
+      </c>
+      <c r="F1494">
+        <f t="shared" si="11"/>
+        <v>5.2431401367187496</v>
+      </c>
+      <c r="G1494">
+        <v>30672262</v>
+      </c>
+      <c r="H1494">
+        <v>30672262</v>
+      </c>
+    </row>
+    <row r="1495" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1495" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B1495">
+        <v>5266.27978515625</v>
+      </c>
+      <c r="C1495">
+        <v>5354.8359375</v>
+      </c>
+      <c r="D1495">
+        <v>5256.02001953125</v>
+      </c>
+      <c r="E1495">
+        <v>5352.708984375</v>
+      </c>
+      <c r="F1495">
+        <f t="shared" si="11"/>
+        <v>5.352708984375</v>
+      </c>
+      <c r="G1495">
+        <v>32440512</v>
+      </c>
+      <c r="H1495">
+        <v>32440512</v>
+      </c>
+    </row>
+    <row r="1496" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1496" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B1496">
+        <v>5395.39501953125</v>
+      </c>
+      <c r="C1496">
+        <v>5403.4609375</v>
+      </c>
+      <c r="D1496">
+        <v>5280.419921875</v>
+      </c>
+      <c r="E1496">
+        <v>5307.630859375</v>
+      </c>
+      <c r="F1496">
+        <f t="shared" si="11"/>
+        <v>5.3076308593750001</v>
+      </c>
+      <c r="G1496">
+        <v>30606808</v>
+      </c>
+      <c r="H1496">
+        <v>30606808</v>
+      </c>
+    </row>
+    <row r="1497" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1497" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B1497">
+        <v>5331.53515625</v>
+      </c>
+      <c r="C1497">
+        <v>5427.11083984375</v>
+      </c>
+      <c r="D1497">
+        <v>5309.52001953125</v>
+      </c>
+      <c r="E1497">
+        <v>5422.06298828125</v>
+      </c>
+      <c r="F1497">
+        <f t="shared" si="11"/>
+        <v>5.4220629882812501</v>
+      </c>
+      <c r="G1497">
+        <v>32936314</v>
+      </c>
+      <c r="H1497">
+        <v>32936314</v>
+      </c>
+    </row>
+    <row r="1498" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1498" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B1498">
+        <v>5446.7490234375</v>
+      </c>
+      <c r="C1498">
+        <v>5470.19384765625</v>
+      </c>
+      <c r="D1498">
+        <v>5419.28076171875</v>
+      </c>
+      <c r="E1498">
+        <v>5454.61083984375</v>
+      </c>
+      <c r="F1498">
+        <f t="shared" si="11"/>
+        <v>5.4546108398437498</v>
+      </c>
+      <c r="G1498">
+        <v>32407686</v>
+      </c>
+      <c r="H1498">
+        <v>32407686</v>
+      </c>
+    </row>
+    <row r="1499" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1499" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B1499">
+        <v>5437.72509765625</v>
+      </c>
+      <c r="C1499">
+        <v>5510.89404296875</v>
+      </c>
+      <c r="D1499">
+        <v>5418.02099609375</v>
+      </c>
+      <c r="E1499">
+        <v>5482.00390625</v>
+      </c>
+      <c r="F1499">
+        <f t="shared" si="11"/>
+        <v>5.4820039062500001</v>
+      </c>
+      <c r="G1499">
+        <v>35480500</v>
+      </c>
+      <c r="H1499">
+        <v>35480500</v>
+      </c>
+    </row>
+    <row r="1500" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1500" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B1500">
+        <v>5472.73681640625</v>
+      </c>
+      <c r="C1500">
+        <v>5501.96923828125</v>
+      </c>
+      <c r="D1500">
+        <v>5401.69384765625</v>
+      </c>
+      <c r="E1500">
+        <v>5492.9990234375</v>
+      </c>
+      <c r="F1500">
+        <f t="shared" si="11"/>
+        <v>5.4929990234375001</v>
+      </c>
+      <c r="G1500">
+        <v>31518084</v>
+      </c>
+      <c r="H1500">
+        <v>31518084</v>
+      </c>
+    </row>
+    <row r="1501" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1501" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B1501">
+        <v>5454.9912109375</v>
+      </c>
+      <c r="C1501">
+        <v>5548.88623046875</v>
+      </c>
+      <c r="D1501">
+        <v>5454.9912109375</v>
+      </c>
+      <c r="E1501">
+        <v>5545.48583984375</v>
+      </c>
+      <c r="F1501">
+        <f t="shared" si="11"/>
+        <v>5.5454858398437503</v>
+      </c>
+      <c r="G1501">
+        <v>35979108</v>
+      </c>
+      <c r="H1501">
+        <v>35979108</v>
+      </c>
+    </row>
+    <row r="1502" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1502" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B1502">
+        <v>5565.283203125</v>
+      </c>
+      <c r="C1502">
+        <v>5589.03076171875</v>
+      </c>
+      <c r="D1502">
+        <v>5474.04296875</v>
+      </c>
+      <c r="E1502">
+        <v>5526.51806640625</v>
+      </c>
+      <c r="F1502">
+        <f t="shared" si="11"/>
+        <v>5.5265180664062497</v>
+      </c>
+      <c r="G1502">
+        <v>36807356</v>
+      </c>
+      <c r="H1502">
+        <v>36807356</v>
+      </c>
+    </row>
+    <row r="1503" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1503" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B1503">
+        <v>5517.47412109375</v>
+      </c>
+      <c r="C1503">
+        <v>5536.72802734375</v>
+      </c>
+      <c r="D1503">
+        <v>5455.2529296875</v>
+      </c>
+      <c r="E1503">
+        <v>5504.42919921875</v>
+      </c>
+      <c r="F1503">
+        <f t="shared" si="11"/>
+        <v>5.50442919921875</v>
+      </c>
+      <c r="G1503">
+        <v>32154030</v>
+      </c>
+      <c r="H1503">
+        <v>32154030</v>
+      </c>
+    </row>
+    <row r="1504" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1504" s="1">
+        <v>46139</v>
+      </c>
+      <c r="B1504">
+        <v>5507.72509765625</v>
+      </c>
+      <c r="C1504">
+        <v>5534.43505859375</v>
+      </c>
+      <c r="D1504">
+        <v>5477.73779296875</v>
+      </c>
+      <c r="E1504">
+        <v>5505.6669921875</v>
+      </c>
+      <c r="F1504">
+        <f t="shared" si="11"/>
+        <v>5.5056669921874999</v>
+      </c>
+      <c r="G1504">
+        <v>33859504</v>
+      </c>
+      <c r="H1504">
+        <v>33859504</v>
+      </c>
+    </row>
+    <row r="1505" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1505" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B1505">
+        <v>5458.0478515625</v>
+      </c>
+      <c r="C1505">
+        <v>5476.52880859375</v>
+      </c>
+      <c r="D1505">
+        <v>5400.56396484375</v>
+      </c>
+      <c r="E1505">
+        <v>5417.94189453125</v>
+      </c>
+      <c r="F1505">
+        <f t="shared" si="11"/>
+        <v>5.4179418945312499</v>
+      </c>
+      <c r="G1505">
+        <v>34549588</v>
+      </c>
+      <c r="H1505">
+        <v>34549588</v>
+      </c>
+    </row>
+    <row r="1506" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1506" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B1506">
+        <v>5391.0732421875</v>
+      </c>
+      <c r="C1506">
+        <v>5530.94482421875</v>
+      </c>
+      <c r="D1506">
+        <v>5391.0732421875</v>
+      </c>
+      <c r="E1506">
+        <v>5524.14892578125</v>
+      </c>
+      <c r="F1506">
+        <f t="shared" si="11"/>
+        <v>5.5241489257812502</v>
+      </c>
+      <c r="G1506">
+        <v>32672834</v>
+      </c>
+      <c r="H1506">
+        <v>32672834</v>
+      </c>
+    </row>
+    <row r="1507" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1507" s="1">
+        <v>46142</v>
+      </c>
+      <c r="B1507">
+        <v>5546.4580078125</v>
+      </c>
+      <c r="C1507">
+        <v>5570.34814453125</v>
+      </c>
+      <c r="D1507">
+        <v>5521.80810546875</v>
+      </c>
+      <c r="E1507">
+        <v>5545.80810546875</v>
+      </c>
+      <c r="F1507">
+        <f t="shared" si="11"/>
+        <v>5.5458081054687502</v>
+      </c>
+      <c r="G1507">
+        <v>35149036</v>
+      </c>
+      <c r="H1507">
+        <v>35149036</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100index.xlsx
+++ b/lai/valuationquan/szseinnovation100index.xlsx
@@ -400,7 +400,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:H1507"/>
+  <dimension ref="A1:H1525"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="9" max="9" width="9.5" bestFit="1" customWidth="1"/>
@@ -40006,7 +40006,7 @@
         <v>5027.0078125</v>
       </c>
       <c r="F1468">
-        <f t="shared" ref="F1468:F1507" si="11">E1468/1000</f>
+        <f t="shared" ref="F1468:F1525" si="11">E1468/1000</f>
         <v>5.0270078125</v>
       </c>
       <c r="G1468">
@@ -41067,6 +41067,492 @@
       </c>
       <c r="H1507">
         <v>35149036</v>
+      </c>
+    </row>
+    <row r="1508" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1508" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B1508">
+        <v>5650.09619140625</v>
+      </c>
+      <c r="C1508">
+        <v>5713.77294921875</v>
+      </c>
+      <c r="D1508">
+        <v>5600.43408203125</v>
+      </c>
+      <c r="E1508">
+        <v>5669.85302734375</v>
+      </c>
+      <c r="F1508">
+        <f t="shared" si="11"/>
+        <v>5.6698530273437502</v>
+      </c>
+      <c r="G1508">
+        <v>41654332</v>
+      </c>
+      <c r="H1508">
+        <v>41654332</v>
+      </c>
+    </row>
+    <row r="1509" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1509" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B1509">
+        <v>5714.56982421875</v>
+      </c>
+      <c r="C1509">
+        <v>5744.9169921875</v>
+      </c>
+      <c r="D1509">
+        <v>5658.4501953125</v>
+      </c>
+      <c r="E1509">
+        <v>5733.97509765625</v>
+      </c>
+      <c r="F1509">
+        <f t="shared" si="11"/>
+        <v>5.7339750976562502</v>
+      </c>
+      <c r="G1509">
+        <v>38461288</v>
+      </c>
+      <c r="H1509">
+        <v>38461288</v>
+      </c>
+    </row>
+    <row r="1510" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1510" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B1510">
+        <v>5691.40380859375</v>
+      </c>
+      <c r="C1510">
+        <v>5732.94921875</v>
+      </c>
+      <c r="D1510">
+        <v>5672.4609375</v>
+      </c>
+      <c r="E1510">
+        <v>5712.59423828125</v>
+      </c>
+      <c r="F1510">
+        <f t="shared" si="11"/>
+        <v>5.71259423828125</v>
+      </c>
+      <c r="G1510">
+        <v>36765044</v>
+      </c>
+      <c r="H1510">
+        <v>36765044</v>
+      </c>
+    </row>
+    <row r="1511" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1511" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B1511">
+        <v>5754.0859375</v>
+      </c>
+      <c r="C1511">
+        <v>5887.82177734375</v>
+      </c>
+      <c r="D1511">
+        <v>5737.60595703125</v>
+      </c>
+      <c r="E1511">
+        <v>5878.8681640625</v>
+      </c>
+      <c r="F1511">
+        <f t="shared" si="11"/>
+        <v>5.8788681640625002</v>
+      </c>
+      <c r="G1511">
+        <v>49346068</v>
+      </c>
+      <c r="H1511">
+        <v>49346068</v>
+      </c>
+    </row>
+    <row r="1512" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1512" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B1512">
+        <v>5896.3251953125</v>
+      </c>
+      <c r="C1512">
+        <v>5901.0068359375</v>
+      </c>
+      <c r="D1512">
+        <v>5840.296875</v>
+      </c>
+      <c r="E1512">
+        <v>5883.4228515625</v>
+      </c>
+      <c r="F1512">
+        <f t="shared" si="11"/>
+        <v>5.8834228515625</v>
+      </c>
+      <c r="G1512">
+        <v>41127148</v>
+      </c>
+      <c r="H1512">
+        <v>41127148</v>
+      </c>
+    </row>
+    <row r="1513" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1513" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B1513">
+        <v>5839.80908203125</v>
+      </c>
+      <c r="C1513">
+        <v>5993.53515625</v>
+      </c>
+      <c r="D1513">
+        <v>5833.3408203125</v>
+      </c>
+      <c r="E1513">
+        <v>5986.98388671875</v>
+      </c>
+      <c r="F1513">
+        <f t="shared" si="11"/>
+        <v>5.9869838867187504</v>
+      </c>
+      <c r="G1513">
+        <v>39922696</v>
+      </c>
+      <c r="H1513">
+        <v>39922696</v>
+      </c>
+    </row>
+    <row r="1514" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1514" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B1514">
+        <v>6053.1201171875</v>
+      </c>
+      <c r="C1514">
+        <v>6058.8349609375</v>
+      </c>
+      <c r="D1514">
+        <v>5870.60302734375</v>
+      </c>
+      <c r="E1514">
+        <v>5897.17578125</v>
+      </c>
+      <c r="F1514">
+        <f t="shared" si="11"/>
+        <v>5.8971757812499996</v>
+      </c>
+      <c r="G1514">
+        <v>40727936</v>
+      </c>
+      <c r="H1514">
+        <v>40727936</v>
+      </c>
+    </row>
+    <row r="1515" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1515" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B1515">
+        <v>5900.2138671875</v>
+      </c>
+      <c r="C1515">
+        <v>5977.80419921875</v>
+      </c>
+      <c r="D1515">
+        <v>5785.34716796875</v>
+      </c>
+      <c r="E1515">
+        <v>5871.091796875</v>
+      </c>
+      <c r="F1515">
+        <f t="shared" si="11"/>
+        <v>5.8710917968749996</v>
+      </c>
+      <c r="G1515">
+        <v>44799476</v>
+      </c>
+      <c r="H1515">
+        <v>44799476</v>
+      </c>
+    </row>
+    <row r="1516" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1516" s="1">
+        <v>46160</v>
+      </c>
+      <c r="B1516">
+        <v>5836.09814453125</v>
+      </c>
+      <c r="C1516">
+        <v>5943.73388671875</v>
+      </c>
+      <c r="D1516">
+        <v>5833.52685546875</v>
+      </c>
+      <c r="E1516">
+        <v>5874.90283203125</v>
+      </c>
+      <c r="F1516">
+        <f t="shared" si="11"/>
+        <v>5.8749028320312497</v>
+      </c>
+      <c r="G1516">
+        <v>37543556</v>
+      </c>
+      <c r="H1516">
+        <v>37543556</v>
+      </c>
+    </row>
+    <row r="1517" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1517" s="1">
+        <v>46161</v>
+      </c>
+      <c r="B1517">
+        <v>5849.4609375</v>
+      </c>
+      <c r="C1517">
+        <v>5910.85009765625</v>
+      </c>
+      <c r="D1517">
+        <v>5759.0380859375</v>
+      </c>
+      <c r="E1517">
+        <v>5904.51806640625</v>
+      </c>
+      <c r="F1517">
+        <f t="shared" si="11"/>
+        <v>5.9045180664062498</v>
+      </c>
+      <c r="G1517">
+        <v>34695180</v>
+      </c>
+      <c r="H1517">
+        <v>34695180</v>
+      </c>
+    </row>
+    <row r="1518" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1518" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B1518">
+        <v>5869.0048828125</v>
+      </c>
+      <c r="C1518">
+        <v>5953.69580078125</v>
+      </c>
+      <c r="D1518">
+        <v>5866.4970703125</v>
+      </c>
+      <c r="E1518">
+        <v>5932.85205078125</v>
+      </c>
+      <c r="F1518">
+        <f t="shared" si="11"/>
+        <v>5.9328520507812499</v>
+      </c>
+      <c r="G1518">
+        <v>35275012</v>
+      </c>
+      <c r="H1518">
+        <v>35275012</v>
+      </c>
+    </row>
+    <row r="1519" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1519" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B1519">
+        <v>5989.58984375</v>
+      </c>
+      <c r="C1519">
+        <v>6086.56298828125</v>
+      </c>
+      <c r="D1519">
+        <v>5828.27099609375</v>
+      </c>
+      <c r="E1519">
+        <v>5833.27490234375</v>
+      </c>
+      <c r="F1519">
+        <f t="shared" si="11"/>
+        <v>5.8332749023437502</v>
+      </c>
+      <c r="G1519">
+        <v>49524404</v>
+      </c>
+      <c r="H1519">
+        <v>49524404</v>
+      </c>
+    </row>
+    <row r="1520" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1520" s="1">
+        <v>46164</v>
+      </c>
+      <c r="B1520">
+        <v>5870.89892578125</v>
+      </c>
+      <c r="C1520">
+        <v>5935.84619140625</v>
+      </c>
+      <c r="D1520">
+        <v>5830.35498046875</v>
+      </c>
+      <c r="E1520">
+        <v>5922.94287109375</v>
+      </c>
+      <c r="F1520">
+        <f t="shared" si="11"/>
+        <v>5.92294287109375</v>
+      </c>
+      <c r="G1520">
+        <v>38068636</v>
+      </c>
+      <c r="H1520">
+        <v>38068636</v>
+      </c>
+    </row>
+    <row r="1521" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1521" s="1">
+        <v>46167</v>
+      </c>
+      <c r="B1521">
+        <v>5962.35888671875</v>
+      </c>
+      <c r="C1521">
+        <v>6039.9580078125</v>
+      </c>
+      <c r="D1521">
+        <v>5896.63818359375</v>
+      </c>
+      <c r="E1521">
+        <v>6038.865234375</v>
+      </c>
+      <c r="F1521">
+        <f t="shared" si="11"/>
+        <v>6.0388652343749998</v>
+      </c>
+      <c r="G1521">
+        <v>42237444</v>
+      </c>
+      <c r="H1521">
+        <v>42237444</v>
+      </c>
+    </row>
+    <row r="1522" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1522" s="1">
+        <v>46168</v>
+      </c>
+      <c r="B1522">
+        <v>6022.4228515625</v>
+      </c>
+      <c r="C1522">
+        <v>6061.55322265625</v>
+      </c>
+      <c r="D1522">
+        <v>5954.36083984375</v>
+      </c>
+      <c r="E1522">
+        <v>6028.98486328125</v>
+      </c>
+      <c r="F1522">
+        <f t="shared" si="11"/>
+        <v>6.0289848632812504</v>
+      </c>
+      <c r="G1522">
+        <v>44061652</v>
+      </c>
+      <c r="H1522">
+        <v>44061652</v>
+      </c>
+    </row>
+    <row r="1523" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1523" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B1523">
+        <v>6030.40087890625</v>
+      </c>
+      <c r="C1523">
+        <v>6145.97509765625</v>
+      </c>
+      <c r="D1523">
+        <v>5974.52001953125</v>
+      </c>
+      <c r="E1523">
+        <v>6008.248046875</v>
+      </c>
+      <c r="F1523">
+        <f t="shared" si="11"/>
+        <v>6.0082480468749999</v>
+      </c>
+      <c r="G1523">
+        <v>43522160</v>
+      </c>
+      <c r="H1523">
+        <v>43522160</v>
+      </c>
+    </row>
+    <row r="1524" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1524" s="1">
+        <v>46170</v>
+      </c>
+      <c r="B1524">
+        <v>5993.81787109375</v>
+      </c>
+      <c r="C1524">
+        <v>6122.81103515625</v>
+      </c>
+      <c r="D1524">
+        <v>5923.705078125</v>
+      </c>
+      <c r="E1524">
+        <v>6117.341796875</v>
+      </c>
+      <c r="F1524">
+        <f t="shared" si="11"/>
+        <v>6.1173417968750003</v>
+      </c>
+      <c r="G1524">
+        <v>41188648</v>
+      </c>
+      <c r="H1524">
+        <v>41188648</v>
+      </c>
+    </row>
+    <row r="1525" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1525" s="1">
+        <v>46171</v>
+      </c>
+      <c r="B1525">
+        <v>6143.85400390625</v>
+      </c>
+      <c r="C1525">
+        <v>6152.2470703125</v>
+      </c>
+      <c r="D1525">
+        <v>5938.2587890625</v>
+      </c>
+      <c r="E1525">
+        <v>5970.703125</v>
+      </c>
+      <c r="F1525">
+        <f t="shared" si="11"/>
+        <v>5.970703125</v>
+      </c>
+      <c r="G1525">
+        <v>44577412</v>
+      </c>
+      <c r="H1525">
+        <v>44577412</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100index.xlsx
+++ b/lai/valuationquan/szseinnovation100index.xlsx
@@ -400,7 +400,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:H1525"/>
+  <dimension ref="A1:H1546"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="9" max="9" width="9.5" bestFit="1" customWidth="1"/>
@@ -40006,7 +40006,7 @@
         <v>5027.0078125</v>
       </c>
       <c r="F1468">
-        <f t="shared" ref="F1468:F1525" si="11">E1468/1000</f>
+        <f t="shared" ref="F1468:F1546" si="11">E1468/1000</f>
         <v>5.0270078125</v>
       </c>
       <c r="G1468">
@@ -41553,6 +41553,573 @@
       </c>
       <c r="H1525">
         <v>44577412</v>
+      </c>
+    </row>
+    <row r="1526" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1526" s="1">
+        <v>46174</v>
+      </c>
+      <c r="B1526">
+        <v>5995.18798828125</v>
+      </c>
+      <c r="C1526">
+        <v>6019.47119140625</v>
+      </c>
+      <c r="D1526">
+        <v>5847.27392578125</v>
+      </c>
+      <c r="E1526">
+        <v>5859.97216796875</v>
+      </c>
+      <c r="F1526">
+        <f t="shared" si="11"/>
+        <v>5.85997216796875</v>
+      </c>
+      <c r="G1526">
+        <v>35498252</v>
+      </c>
+      <c r="H1526">
+        <v>35498252</v>
+      </c>
+    </row>
+    <row r="1527" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1527" s="1">
+        <v>46175</v>
+      </c>
+      <c r="B1527">
+        <v>5909.23486328125</v>
+      </c>
+      <c r="C1527">
+        <v>6018.76708984375</v>
+      </c>
+      <c r="D1527">
+        <v>5837.0400390625</v>
+      </c>
+      <c r="E1527">
+        <v>5983.55712890625</v>
+      </c>
+      <c r="F1527">
+        <f t="shared" si="11"/>
+        <v>5.9835571289062504</v>
+      </c>
+      <c r="G1527">
+        <v>33976524</v>
+      </c>
+      <c r="H1527">
+        <v>33976524</v>
+      </c>
+    </row>
+    <row r="1528" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1528" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B1528">
+        <v>6010.01611328125</v>
+      </c>
+      <c r="C1528">
+        <v>6178.47802734375</v>
+      </c>
+      <c r="D1528">
+        <v>5994.61279296875</v>
+      </c>
+      <c r="E1528">
+        <v>6065.4482421875</v>
+      </c>
+      <c r="F1528">
+        <f t="shared" si="11"/>
+        <v>6.0654482421875002</v>
+      </c>
+      <c r="G1528">
+        <v>40395228</v>
+      </c>
+      <c r="H1528">
+        <v>40395228</v>
+      </c>
+    </row>
+    <row r="1529" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1529" s="1">
+        <v>46177</v>
+      </c>
+      <c r="B1529">
+        <v>5997.9560546875</v>
+      </c>
+      <c r="C1529">
+        <v>6075.990234375</v>
+      </c>
+      <c r="D1529">
+        <v>5984.3359375</v>
+      </c>
+      <c r="E1529">
+        <v>6033.423828125</v>
+      </c>
+      <c r="F1529">
+        <f t="shared" si="11"/>
+        <v>6.0334238281249997</v>
+      </c>
+      <c r="G1529">
+        <v>37498108</v>
+      </c>
+      <c r="H1529">
+        <v>37498108</v>
+      </c>
+    </row>
+    <row r="1530" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1530" s="1">
+        <v>46178</v>
+      </c>
+      <c r="B1530">
+        <v>6011.73681640625</v>
+      </c>
+      <c r="C1530">
+        <v>6045.2978515625</v>
+      </c>
+      <c r="D1530">
+        <v>5841.69677734375</v>
+      </c>
+      <c r="E1530">
+        <v>5870.9970703125</v>
+      </c>
+      <c r="F1530">
+        <f t="shared" si="11"/>
+        <v>5.8709970703124998</v>
+      </c>
+      <c r="G1530">
+        <v>43405164</v>
+      </c>
+      <c r="H1530">
+        <v>43405164</v>
+      </c>
+    </row>
+    <row r="1531" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1531" s="1">
+        <v>46181</v>
+      </c>
+      <c r="B1531">
+        <v>5687.2041015625</v>
+      </c>
+      <c r="C1531">
+        <v>5821.15478515625</v>
+      </c>
+      <c r="D1531">
+        <v>5650.30419921875</v>
+      </c>
+      <c r="E1531">
+        <v>5697.2578125</v>
+      </c>
+      <c r="F1531">
+        <f t="shared" si="11"/>
+        <v>5.6972578125000002</v>
+      </c>
+      <c r="G1531">
+        <v>39537772</v>
+      </c>
+      <c r="H1531">
+        <v>39537772</v>
+      </c>
+    </row>
+    <row r="1532" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1532" s="1">
+        <v>46182</v>
+      </c>
+      <c r="B1532">
+        <v>5750.01708984375</v>
+      </c>
+      <c r="C1532">
+        <v>5845.43408203125</v>
+      </c>
+      <c r="D1532">
+        <v>5682.2109375</v>
+      </c>
+      <c r="E1532">
+        <v>5839.3291015625</v>
+      </c>
+      <c r="F1532">
+        <f t="shared" si="11"/>
+        <v>5.8393291015625</v>
+      </c>
+      <c r="G1532">
+        <v>36339236</v>
+      </c>
+      <c r="H1532">
+        <v>36339236</v>
+      </c>
+    </row>
+    <row r="1533" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1533" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B1533">
+        <v>5757.35302734375</v>
+      </c>
+      <c r="C1533">
+        <v>5790.02490234375</v>
+      </c>
+      <c r="D1533">
+        <v>5660.02978515625</v>
+      </c>
+      <c r="E1533">
+        <v>5708.955078125</v>
+      </c>
+      <c r="F1533">
+        <f t="shared" si="11"/>
+        <v>5.7089550781250002</v>
+      </c>
+      <c r="G1533">
+        <v>36098620</v>
+      </c>
+      <c r="H1533">
+        <v>36098620</v>
+      </c>
+    </row>
+    <row r="1534" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1534" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B1534">
+        <v>5675.89892578125</v>
+      </c>
+      <c r="C1534">
+        <v>5775.4912109375</v>
+      </c>
+      <c r="D1534">
+        <v>5614.72216796875</v>
+      </c>
+      <c r="E1534">
+        <v>5671.86376953125</v>
+      </c>
+      <c r="F1534">
+        <f t="shared" si="11"/>
+        <v>5.6718637695312504</v>
+      </c>
+      <c r="G1534">
+        <v>35614492</v>
+      </c>
+      <c r="H1534">
+        <v>35614492</v>
+      </c>
+    </row>
+    <row r="1535" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1535" s="1">
+        <v>46185</v>
+      </c>
+      <c r="B1535">
+        <v>5808.44287109375</v>
+      </c>
+      <c r="C1535">
+        <v>5811.97021484375</v>
+      </c>
+      <c r="D1535">
+        <v>5717.6328125</v>
+      </c>
+      <c r="E1535">
+        <v>5729.0849609375</v>
+      </c>
+      <c r="F1535">
+        <f t="shared" si="11"/>
+        <v>5.7290849609374996</v>
+      </c>
+      <c r="G1535">
+        <v>45302608</v>
+      </c>
+      <c r="H1535">
+        <v>45302608</v>
+      </c>
+    </row>
+    <row r="1536" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1536" s="1">
+        <v>46188</v>
+      </c>
+      <c r="B1536">
+        <v>5799.1728515625</v>
+      </c>
+      <c r="C1536">
+        <v>5949.240234375</v>
+      </c>
+      <c r="D1536">
+        <v>5739.4990234375</v>
+      </c>
+      <c r="E1536">
+        <v>5948.74609375</v>
+      </c>
+      <c r="F1536">
+        <f t="shared" si="11"/>
+        <v>5.9487460937499996</v>
+      </c>
+      <c r="G1536">
+        <v>43783524</v>
+      </c>
+      <c r="H1536">
+        <v>43783524</v>
+      </c>
+    </row>
+    <row r="1537" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1537" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B1537">
+        <v>5998.97216796875</v>
+      </c>
+      <c r="C1537">
+        <v>6069.080078125</v>
+      </c>
+      <c r="D1537">
+        <v>5976.68115234375</v>
+      </c>
+      <c r="E1537">
+        <v>6043.68408203125</v>
+      </c>
+      <c r="F1537">
+        <f t="shared" si="11"/>
+        <v>6.0436840820312501</v>
+      </c>
+      <c r="G1537">
+        <v>45488828</v>
+      </c>
+      <c r="H1537">
+        <v>45488828</v>
+      </c>
+    </row>
+    <row r="1538" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1538" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B1538">
+        <v>5993.4990234375</v>
+      </c>
+      <c r="C1538">
+        <v>6132.759765625</v>
+      </c>
+      <c r="D1538">
+        <v>5993.4990234375</v>
+      </c>
+      <c r="E1538">
+        <v>6131.546875</v>
+      </c>
+      <c r="F1538">
+        <f t="shared" si="11"/>
+        <v>6.1315468749999997</v>
+      </c>
+      <c r="G1538">
+        <v>42465324</v>
+      </c>
+      <c r="H1538">
+        <v>42465324</v>
+      </c>
+    </row>
+    <row r="1539" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1539" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B1539">
+        <v>6111.07080078125</v>
+      </c>
+      <c r="C1539">
+        <v>6251.4189453125</v>
+      </c>
+      <c r="D1539">
+        <v>6110.97216796875</v>
+      </c>
+      <c r="E1539">
+        <v>6225.880859375</v>
+      </c>
+      <c r="F1539">
+        <f t="shared" si="11"/>
+        <v>6.2258808593749997</v>
+      </c>
+      <c r="G1539">
+        <v>42574980</v>
+      </c>
+      <c r="H1539">
+        <v>42574980</v>
+      </c>
+    </row>
+    <row r="1540" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1540" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B1540">
+        <v>6259.35107421875</v>
+      </c>
+      <c r="C1540">
+        <v>6381.02392578125</v>
+      </c>
+      <c r="D1540">
+        <v>6188.77392578125</v>
+      </c>
+      <c r="E1540">
+        <v>6380.0078125</v>
+      </c>
+      <c r="F1540">
+        <f t="shared" si="11"/>
+        <v>6.3800078124999997</v>
+      </c>
+      <c r="G1540">
+        <v>58412476</v>
+      </c>
+      <c r="H1540">
+        <v>58412476</v>
+      </c>
+    </row>
+    <row r="1541" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1541" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B1541">
+        <v>6385.4072265625</v>
+      </c>
+      <c r="C1541">
+        <v>6389.64013671875</v>
+      </c>
+      <c r="D1541">
+        <v>6138.0791015625</v>
+      </c>
+      <c r="E1541">
+        <v>6178.951171875</v>
+      </c>
+      <c r="F1541">
+        <f t="shared" si="11"/>
+        <v>6.1789511718750001</v>
+      </c>
+      <c r="G1541">
+        <v>52420400</v>
+      </c>
+      <c r="H1541">
+        <v>52420400</v>
+      </c>
+    </row>
+    <row r="1542" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1542" s="1">
+        <v>46197</v>
+      </c>
+      <c r="B1542">
+        <v>6141.7001953125</v>
+      </c>
+      <c r="C1542">
+        <v>6258.72314453125</v>
+      </c>
+      <c r="D1542">
+        <v>6112.0771484375</v>
+      </c>
+      <c r="E1542">
+        <v>6246.373046875</v>
+      </c>
+      <c r="F1542">
+        <f t="shared" si="11"/>
+        <v>6.2463730468750001</v>
+      </c>
+      <c r="G1542">
+        <v>46890936</v>
+      </c>
+      <c r="H1542">
+        <v>46890936</v>
+      </c>
+    </row>
+    <row r="1543" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1543" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B1543">
+        <v>6276.06005859375</v>
+      </c>
+      <c r="C1543">
+        <v>6358.3330078125</v>
+      </c>
+      <c r="D1543">
+        <v>6246.54296875</v>
+      </c>
+      <c r="E1543">
+        <v>6344.64306640625</v>
+      </c>
+      <c r="F1543">
+        <f t="shared" si="11"/>
+        <v>6.3446430664062499</v>
+      </c>
+      <c r="G1543">
+        <v>52301836</v>
+      </c>
+      <c r="H1543">
+        <v>52301836</v>
+      </c>
+    </row>
+    <row r="1544" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1544" s="1">
+        <v>46199</v>
+      </c>
+      <c r="B1544">
+        <v>6304.544921875</v>
+      </c>
+      <c r="C1544">
+        <v>6304.544921875</v>
+      </c>
+      <c r="D1544">
+        <v>6068.57421875</v>
+      </c>
+      <c r="E1544">
+        <v>6085.85498046875</v>
+      </c>
+      <c r="F1544">
+        <f t="shared" si="11"/>
+        <v>6.0858549804687501</v>
+      </c>
+      <c r="G1544">
+        <v>48984644</v>
+      </c>
+      <c r="H1544">
+        <v>48984644</v>
+      </c>
+    </row>
+    <row r="1545" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1545" s="1">
+        <v>46202</v>
+      </c>
+      <c r="B1545">
+        <v>6096.38916015625</v>
+      </c>
+      <c r="C1545">
+        <v>6170.68701171875</v>
+      </c>
+      <c r="D1545">
+        <v>5951.4541015625</v>
+      </c>
+      <c r="E1545">
+        <v>6104.8310546875</v>
+      </c>
+      <c r="F1545">
+        <f t="shared" si="11"/>
+        <v>6.1048310546874998</v>
+      </c>
+      <c r="G1545">
+        <v>45607440</v>
+      </c>
+      <c r="H1545">
+        <v>45607440</v>
+      </c>
+    </row>
+    <row r="1546" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A1546" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B1546">
+        <v>6123.8681640625</v>
+      </c>
+      <c r="C1546">
+        <v>6302.76220703125</v>
+      </c>
+      <c r="D1546">
+        <v>6122.669921875</v>
+      </c>
+      <c r="E1546">
+        <v>6276.416015625</v>
+      </c>
+      <c r="F1546">
+        <f t="shared" si="11"/>
+        <v>6.2764160156250002</v>
+      </c>
+      <c r="G1546">
+        <v>42918828</v>
+      </c>
+      <c r="H1546">
+        <v>42918828</v>
       </c>
     </row>
   </sheetData>
